--- a/output/central_unit_requests/L&R - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/L&R - SR26 sustainability reporting request.xlsx
@@ -633,7 +633,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/L&R - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/L&R - SR26 sustainability reporting request.xlsx
@@ -31,7 +31,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -110,7 +110,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,9 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -297,6 +305,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -608,24 +706,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -633,7 +768,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -644,7 +779,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Legal &amp; Risk – Risk &amp; resilience</t>
         </is>
@@ -652,163 +787,163 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="204" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Climate leadership</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Reach and maintain high levels of climate-change resilience maturity</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Maturity assessment of the University’s preparedness for climate-related impacts and capability to respond, assessed across relevant organisational functions:
 o	Governance and strategy
@@ -820,46 +955,46 @@
 o	Financial planning and reporting.</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 8a(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available
+In end-2025 reporting your area reported on the related SP2030 target 8a(i) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will report the University's climate-change resilience maturity rating, key gaps and priority actions in the 2026 Sustainability Report (building on the Climate Change Preparedness Framework assessment reported in 2025).</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>8a(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>Review of University Risk 16 Climate Change was completed in Nov 2025, as part of the annual review cycle.
 The review identified a positive trend, showing improved levels of climate‑change preparedness, with work underway to complete the end‑of‑2025 assessment.</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>All University risks including Risk 16 Climate Change were presented to RMCC and ARC in Nov 25 for their oversight.
 There will be a risk presentation of Risk 16 Climate Change at RMCC Meeting 1 in Feb 2026.</t>
         </is>
       </c>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17"/>
   </sheetData>
@@ -879,6 +1014,7 @@
     <hyperlink ref="H16" location="'3. SR25 responses'!B7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -888,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -901,104 +1037,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1006,6 +1186,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1015,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1027,154 +1208,199 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Legal and Risk</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Legal and Risk</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>8a(i)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Assessment based on the Climate Change Preparedness Framework</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>Review of University Risk 16 Climate Change was completed in Nov 2025, as part of the annual review cycle.
 The review identified a positive trend, showing improved levels of climate‑change preparedness, with work underway to complete the end‑of‑2025 assessment.</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>All University risks including Risk 16 Climate Change were presented to RMCC and ARC in Nov 25 for their oversight.
 There will be a risk presentation of Risk 16 Climate Change at RMCC Meeting 1 in Feb 2026.</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>CL3(a)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>8a(ii)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>The University reaches and maintains a 'high' climate change preparedness level</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Case studies demonstrating climate change preparedness</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>Flood Emergency Response Plans (FERP) for Southbank - MCM has been completed, while MTC is still in progress.
 The FERP for Creswick has also been completed and is awaiting review by FM Global.
 Case study -  In 2025, UoM received approximately $229k in resilience credits from FM Global, which can be applied to climate‑related projects.</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>As part of the University’s ongoing commitment to strengthening preparedness for climate‑related events, these FERPs will be reviewed regularly by both UoM  and FM Global. Ongoing training and awareness are also essential to ensuring the effectiveness of these plans.</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1184,6 +1410,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/central_unit_requests/L&R - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/L&R - SR26 sustainability reporting request.xlsx
@@ -703,9 +703,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -764,7 +764,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -803,7 +804,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -871,17 +872,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -913,17 +904,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -993,23 +974,16 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B7"/>
   </hyperlinks>
